--- a/data/Jam_table.xlsx
+++ b/data/Jam_table.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Documents\Radical_stats\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Proyectos\Radical_stats\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F23FA2B-3E9B-49D8-8B9B-D8F17D15CA42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E4B620-305A-49B2-A58E-BA256EFF1E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{BF9B31FC-DB18-486C-BF79-DC3311B75936}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Jam" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Jam!$A$1:$L$124</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="20">
   <si>
     <t>Jam</t>
   </si>
@@ -44,13 +44,13 @@
     <t>Jammer</t>
   </si>
   <si>
+    <t>Lost</t>
+  </si>
+  <si>
     <t>Lider</t>
   </si>
   <si>
     <t>Call</t>
-  </si>
-  <si>
-    <t>Lost</t>
   </si>
   <si>
     <t>Injury</t>
@@ -65,16 +65,19 @@
     <t>Star_pass</t>
   </si>
   <si>
+    <t>Period</t>
+  </si>
+  <si>
     <t>Rival</t>
   </si>
   <si>
-    <t>Pacha Mamis</t>
-  </si>
-  <si>
-    <t>Period</t>
+    <t>Date</t>
   </si>
   <si>
     <t>16</t>
+  </si>
+  <si>
+    <t>Pacha Mamis</t>
   </si>
   <si>
     <t>87</t>
@@ -83,7 +86,16 @@
     <t>26</t>
   </si>
   <si>
-    <t>Date</t>
+    <t>Violet Attack</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>Fuego Latino</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
 </sst>
 </file>
@@ -130,7 +142,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{554484B0-6630-4A06-8BDC-B369FDDAFE7F}"/>
+    <cellStyle name="Excel Built-in Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -462,8 +474,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1832EF2B-6142-46C9-BB38-EDC422D85989}">
-  <dimension ref="A1:L41"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L124"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="7" max="7" width="14.6640625" customWidth="1"/>
@@ -478,13 +490,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
         <v>4</v>
-      </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>3</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -499,13 +511,13 @@
         <v>8</v>
       </c>
       <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
         <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>9</v>
-      </c>
-      <c r="L1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
@@ -540,7 +552,7 @@
         <v>1</v>
       </c>
       <c r="K2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L2" s="1">
         <v>45962</v>
@@ -578,7 +590,7 @@
         <v>1</v>
       </c>
       <c r="K3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L3" s="1">
         <v>45962</v>
@@ -589,7 +601,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -616,7 +628,7 @@
         <v>1</v>
       </c>
       <c r="K4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L4" s="1">
         <v>45962</v>
@@ -654,7 +666,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L5" s="1">
         <v>45962</v>
@@ -665,34 +677,34 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>2</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6" t="s">
         <v>13</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6" t="s">
-        <v>10</v>
       </c>
       <c r="L6" s="1">
         <v>45962</v>
@@ -730,7 +742,7 @@
         <v>1</v>
       </c>
       <c r="K7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L7" s="1">
         <v>45962</v>
@@ -741,34 +753,34 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8" t="s">
         <v>13</v>
-      </c>
-      <c r="C8">
-        <v>0</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>10</v>
       </c>
       <c r="L8" s="1">
         <v>45962</v>
@@ -779,34 +791,34 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9" t="s">
         <v>13</v>
-      </c>
-      <c r="C9">
-        <v>0</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>10</v>
       </c>
       <c r="L9" s="1">
         <v>45962</v>
@@ -844,7 +856,7 @@
         <v>1</v>
       </c>
       <c r="K10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L10" s="1">
         <v>45962</v>
@@ -855,7 +867,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>1</v>
@@ -882,7 +894,7 @@
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L11" s="1">
         <v>45962</v>
@@ -893,7 +905,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12">
         <v>0</v>
@@ -920,7 +932,7 @@
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L12" s="1">
         <v>45962</v>
@@ -931,7 +943,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13">
         <v>0</v>
@@ -958,7 +970,7 @@
         <v>1</v>
       </c>
       <c r="K13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L13" s="1">
         <v>45962</v>
@@ -969,7 +981,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14">
         <v>0</v>
@@ -996,7 +1008,7 @@
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L14" s="1">
         <v>45962</v>
@@ -1034,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="K15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L15" s="1">
         <v>45962</v>
@@ -1045,7 +1057,7 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16">
         <v>0</v>
@@ -1072,7 +1084,7 @@
         <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L16" s="1">
         <v>45962</v>
@@ -1110,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="K17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L17" s="1">
         <v>45962</v>
@@ -1121,7 +1133,7 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18">
         <v>0</v>
@@ -1148,7 +1160,7 @@
         <v>1</v>
       </c>
       <c r="K18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L18" s="1">
         <v>45962</v>
@@ -1186,7 +1198,7 @@
         <v>1</v>
       </c>
       <c r="K19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L19" s="1">
         <v>45962</v>
@@ -1197,7 +1209,7 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C20">
         <v>0</v>
@@ -1224,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L20" s="1">
         <v>45962</v>
@@ -1262,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="K21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L21" s="1">
         <v>45962</v>
@@ -1300,7 +1312,7 @@
         <v>1</v>
       </c>
       <c r="K22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L22" s="1">
         <v>45962</v>
@@ -1338,7 +1350,7 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L23" s="1">
         <v>45962</v>
@@ -1349,7 +1361,7 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C24">
         <v>0</v>
@@ -1376,7 +1388,7 @@
         <v>2</v>
       </c>
       <c r="K24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L24" s="1">
         <v>45962</v>
@@ -1414,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L25" s="1">
         <v>45962</v>
@@ -1425,34 +1437,34 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>2</v>
+      </c>
+      <c r="K26" t="s">
         <v>13</v>
-      </c>
-      <c r="C26">
-        <v>0</v>
-      </c>
-      <c r="D26">
-        <v>0</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-      <c r="F26">
-        <v>0</v>
-      </c>
-      <c r="G26">
-        <v>1</v>
-      </c>
-      <c r="H26">
-        <v>0</v>
-      </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>2</v>
-      </c>
-      <c r="K26" t="s">
-        <v>10</v>
       </c>
       <c r="L26" s="1">
         <v>45962</v>
@@ -1490,7 +1502,7 @@
         <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L27" s="1">
         <v>45962</v>
@@ -1501,7 +1513,7 @@
         <v>5</v>
       </c>
       <c r="B28" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C28">
         <v>0</v>
@@ -1528,7 +1540,7 @@
         <v>2</v>
       </c>
       <c r="K28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L28" s="1">
         <v>45962</v>
@@ -1566,7 +1578,7 @@
         <v>2</v>
       </c>
       <c r="K29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L29" s="1">
         <v>45962</v>
@@ -1577,7 +1589,7 @@
         <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C30">
         <v>0</v>
@@ -1604,7 +1616,7 @@
         <v>2</v>
       </c>
       <c r="K30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L30" s="1">
         <v>45962</v>
@@ -1642,7 +1654,7 @@
         <v>2</v>
       </c>
       <c r="K31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L31" s="1">
         <v>45962</v>
@@ -1653,34 +1665,34 @@
         <v>9</v>
       </c>
       <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32">
+        <v>0</v>
+      </c>
+      <c r="D32">
+        <v>0</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
+        <v>0</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32">
+        <v>0</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>2</v>
+      </c>
+      <c r="K32" t="s">
         <v>13</v>
-      </c>
-      <c r="C32">
-        <v>0</v>
-      </c>
-      <c r="D32">
-        <v>0</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>0</v>
-      </c>
-      <c r="G32">
-        <v>1</v>
-      </c>
-      <c r="H32">
-        <v>0</v>
-      </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>2</v>
-      </c>
-      <c r="K32" t="s">
-        <v>10</v>
       </c>
       <c r="L32" s="1">
         <v>45962</v>
@@ -1718,7 +1730,7 @@
         <v>2</v>
       </c>
       <c r="K33" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L33" s="1">
         <v>45962</v>
@@ -1729,7 +1741,7 @@
         <v>11</v>
       </c>
       <c r="B34" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C34">
         <v>0</v>
@@ -1756,7 +1768,7 @@
         <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L34" s="1">
         <v>45962</v>
@@ -1794,7 +1806,7 @@
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L35" s="1">
         <v>45962</v>
@@ -1832,7 +1844,7 @@
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L36" s="1">
         <v>45962</v>
@@ -1843,7 +1855,7 @@
         <v>14</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C37">
         <v>0</v>
@@ -1870,7 +1882,7 @@
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L37" s="1">
         <v>45962</v>
@@ -1908,7 +1920,7 @@
         <v>2</v>
       </c>
       <c r="K38" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L38" s="1">
         <v>45962</v>
@@ -1919,34 +1931,34 @@
         <v>16</v>
       </c>
       <c r="B39" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="D39">
+        <v>0</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+      <c r="F39">
+        <v>0</v>
+      </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
+      <c r="H39">
+        <v>0</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>2</v>
+      </c>
+      <c r="K39" t="s">
         <v>13</v>
-      </c>
-      <c r="C39">
-        <v>1</v>
-      </c>
-      <c r="D39">
-        <v>0</v>
-      </c>
-      <c r="E39">
-        <v>0</v>
-      </c>
-      <c r="F39">
-        <v>0</v>
-      </c>
-      <c r="G39">
-        <v>0</v>
-      </c>
-      <c r="H39">
-        <v>0</v>
-      </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>2</v>
-      </c>
-      <c r="K39" t="s">
-        <v>10</v>
       </c>
       <c r="L39" s="1">
         <v>45962</v>
@@ -1957,7 +1969,7 @@
         <v>17</v>
       </c>
       <c r="B40" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C40">
         <v>1</v>
@@ -1984,7 +1996,7 @@
         <v>2</v>
       </c>
       <c r="K40" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L40" s="1">
         <v>45962</v>
@@ -1995,40 +2007,3195 @@
         <v>18</v>
       </c>
       <c r="B41" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <v>0</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+      <c r="F41">
+        <v>0</v>
+      </c>
+      <c r="G41">
+        <v>1</v>
+      </c>
+      <c r="H41">
+        <v>0</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>2</v>
+      </c>
+      <c r="K41" t="s">
         <v>13</v>
-      </c>
-      <c r="C41">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <v>0</v>
-      </c>
-      <c r="E41">
-        <v>0</v>
-      </c>
-      <c r="F41">
-        <v>0</v>
-      </c>
-      <c r="G41">
-        <v>1</v>
-      </c>
-      <c r="H41">
-        <v>0</v>
-      </c>
-      <c r="I41">
-        <v>0</v>
-      </c>
-      <c r="J41">
-        <v>2</v>
-      </c>
-      <c r="K41" t="s">
-        <v>10</v>
       </c>
       <c r="L41" s="1">
         <v>45962</v>
       </c>
     </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>1</v>
+      </c>
+      <c r="B42" t="s">
+        <v>12</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42">
+        <v>1</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+      <c r="F42">
+        <v>0</v>
+      </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="K42" t="s">
+        <v>16</v>
+      </c>
+      <c r="L42" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43">
+        <v>0</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+      <c r="H43">
+        <v>11</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="K43" t="s">
+        <v>16</v>
+      </c>
+      <c r="L43" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C44">
+        <v>0</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>4</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>1</v>
+      </c>
+      <c r="K44" t="s">
+        <v>16</v>
+      </c>
+      <c r="L44" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45">
+        <v>0</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>0</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>1</v>
+      </c>
+      <c r="K45" t="s">
+        <v>16</v>
+      </c>
+      <c r="L45" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
+        <v>12</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46">
+        <v>0</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>1</v>
+      </c>
+      <c r="K46" t="s">
+        <v>16</v>
+      </c>
+      <c r="L46" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>6</v>
+      </c>
+      <c r="B47" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47">
+        <v>0</v>
+      </c>
+      <c r="D47">
+        <v>1</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>3</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="K47" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>7</v>
+      </c>
+      <c r="B48" t="s">
+        <v>12</v>
+      </c>
+      <c r="C48">
+        <v>0</v>
+      </c>
+      <c r="D48">
+        <v>0</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>0</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>1</v>
+      </c>
+      <c r="K48" t="s">
+        <v>16</v>
+      </c>
+      <c r="L48" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>8</v>
+      </c>
+      <c r="B49" t="s">
+        <v>15</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>4</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="K49" t="s">
+        <v>16</v>
+      </c>
+      <c r="L49" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>9</v>
+      </c>
+      <c r="B50" t="s">
+        <v>12</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>0</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
+        <v>0</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>1</v>
+      </c>
+      <c r="K50" t="s">
+        <v>16</v>
+      </c>
+      <c r="L50" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51">
+        <v>0</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>1</v>
+      </c>
+      <c r="K51" t="s">
+        <v>16</v>
+      </c>
+      <c r="L51" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>11</v>
+      </c>
+      <c r="B52" t="s">
+        <v>12</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+      <c r="D52">
+        <v>1</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>4</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>1</v>
+      </c>
+      <c r="K52" t="s">
+        <v>16</v>
+      </c>
+      <c r="L52" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>12</v>
+      </c>
+      <c r="B53" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53">
+        <v>0</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>4</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>1</v>
+      </c>
+      <c r="K53" t="s">
+        <v>16</v>
+      </c>
+      <c r="L53" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>13</v>
+      </c>
+      <c r="B54" t="s">
+        <v>12</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>4</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>1</v>
+      </c>
+      <c r="K54" t="s">
+        <v>16</v>
+      </c>
+      <c r="L54" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>14</v>
+      </c>
+      <c r="B55" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55">
+        <v>0</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>4</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>1</v>
+      </c>
+      <c r="K55" t="s">
+        <v>16</v>
+      </c>
+      <c r="L55" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56">
+        <v>0</v>
+      </c>
+      <c r="D56">
+        <v>0</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>16</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>1</v>
+      </c>
+      <c r="K56" t="s">
+        <v>16</v>
+      </c>
+      <c r="L56" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>16</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57">
+        <v>0</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+      <c r="F57">
+        <v>0</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>4</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>1</v>
+      </c>
+      <c r="K57" t="s">
+        <v>16</v>
+      </c>
+      <c r="L57" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>17</v>
+      </c>
+      <c r="B58" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58">
+        <v>0</v>
+      </c>
+      <c r="D58">
+        <v>1</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>12</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58" t="s">
+        <v>16</v>
+      </c>
+      <c r="L58" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>18</v>
+      </c>
+      <c r="B59" t="s">
+        <v>12</v>
+      </c>
+      <c r="C59">
+        <v>1</v>
+      </c>
+      <c r="D59">
+        <v>0</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>1</v>
+      </c>
+      <c r="K59" t="s">
+        <v>16</v>
+      </c>
+      <c r="L59" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>19</v>
+      </c>
+      <c r="B60" t="s">
+        <v>17</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>0</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+      <c r="H60">
+        <v>4</v>
+      </c>
+      <c r="I60">
+        <v>1</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="K60" t="s">
+        <v>16</v>
+      </c>
+      <c r="L60" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>20</v>
+      </c>
+      <c r="B61" t="s">
+        <v>12</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61">
+        <v>0</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>1</v>
+      </c>
+      <c r="K61" t="s">
+        <v>16</v>
+      </c>
+      <c r="L61" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>21</v>
+      </c>
+      <c r="B62" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62">
+        <v>0</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>2</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>1</v>
+      </c>
+      <c r="K62" t="s">
+        <v>16</v>
+      </c>
+      <c r="L62" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>22</v>
+      </c>
+      <c r="B63" t="s">
+        <v>12</v>
+      </c>
+      <c r="C63">
+        <v>0</v>
+      </c>
+      <c r="D63">
+        <v>0</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63" t="s">
+        <v>16</v>
+      </c>
+      <c r="L63" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>23</v>
+      </c>
+      <c r="B64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64">
+        <v>0</v>
+      </c>
+      <c r="D64">
+        <v>1</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>4</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="K64" t="s">
+        <v>16</v>
+      </c>
+      <c r="L64" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>1</v>
+      </c>
+      <c r="B65" t="s">
+        <v>12</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="D65">
+        <v>0</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>7</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>2</v>
+      </c>
+      <c r="K65" t="s">
+        <v>16</v>
+      </c>
+      <c r="L65" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>2</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66">
+        <v>0</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>2</v>
+      </c>
+      <c r="K66" t="s">
+        <v>16</v>
+      </c>
+      <c r="L66" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67">
+        <v>0</v>
+      </c>
+      <c r="D67">
+        <v>0</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>2</v>
+      </c>
+      <c r="K67" t="s">
+        <v>16</v>
+      </c>
+      <c r="L67" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>12</v>
+      </c>
+      <c r="C68">
+        <v>0</v>
+      </c>
+      <c r="D68">
+        <v>0</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>2</v>
+      </c>
+      <c r="K68" t="s">
+        <v>16</v>
+      </c>
+      <c r="L68" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>5</v>
+      </c>
+      <c r="B69" t="s">
+        <v>15</v>
+      </c>
+      <c r="C69">
+        <v>0</v>
+      </c>
+      <c r="D69">
+        <v>0</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>2</v>
+      </c>
+      <c r="K69" t="s">
+        <v>16</v>
+      </c>
+      <c r="L69" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>6</v>
+      </c>
+      <c r="B70" t="s">
+        <v>14</v>
+      </c>
+      <c r="C70">
+        <v>0</v>
+      </c>
+      <c r="D70">
+        <v>1</v>
+      </c>
+      <c r="E70">
+        <v>1</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>8</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>2</v>
+      </c>
+      <c r="K70" t="s">
+        <v>16</v>
+      </c>
+      <c r="L70" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>7</v>
+      </c>
+      <c r="B71" t="s">
+        <v>15</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71">
+        <v>1</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="K71" t="s">
+        <v>16</v>
+      </c>
+      <c r="L71" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>8</v>
+      </c>
+      <c r="B72" t="s">
+        <v>14</v>
+      </c>
+      <c r="C72">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <v>0</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>4</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>2</v>
+      </c>
+      <c r="K72" t="s">
+        <v>16</v>
+      </c>
+      <c r="L72" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <v>1</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>3</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2</v>
+      </c>
+      <c r="K73" t="s">
+        <v>16</v>
+      </c>
+      <c r="L73" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>10</v>
+      </c>
+      <c r="B74" t="s">
+        <v>12</v>
+      </c>
+      <c r="C74">
+        <v>1</v>
+      </c>
+      <c r="D74">
+        <v>0</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
+      <c r="K74" t="s">
+        <v>16</v>
+      </c>
+      <c r="L74" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>11</v>
+      </c>
+      <c r="B75" t="s">
+        <v>12</v>
+      </c>
+      <c r="C75">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <v>0</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>1</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="K75" t="s">
+        <v>16</v>
+      </c>
+      <c r="L75" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>12</v>
+      </c>
+      <c r="B76" t="s">
+        <v>14</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <v>0</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>2</v>
+      </c>
+      <c r="K76" t="s">
+        <v>16</v>
+      </c>
+      <c r="L76" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>13</v>
+      </c>
+      <c r="B77">
+        <v>16</v>
+      </c>
+      <c r="C77">
+        <v>0</v>
+      </c>
+      <c r="D77">
+        <v>0</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>2</v>
+      </c>
+      <c r="K77" t="s">
+        <v>16</v>
+      </c>
+      <c r="L77" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>14</v>
+      </c>
+      <c r="B78" t="s">
+        <v>12</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="E78">
+        <v>1</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>8</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>2</v>
+      </c>
+      <c r="K78" t="s">
+        <v>16</v>
+      </c>
+      <c r="L78" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>14</v>
+      </c>
+      <c r="C79">
+        <v>0</v>
+      </c>
+      <c r="D79">
+        <v>1</v>
+      </c>
+      <c r="E79">
+        <v>1</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="K79" t="s">
+        <v>16</v>
+      </c>
+      <c r="L79" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>16</v>
+      </c>
+      <c r="B80" t="s">
+        <v>12</v>
+      </c>
+      <c r="C80">
+        <v>0</v>
+      </c>
+      <c r="D80">
+        <v>0</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80" t="s">
+        <v>16</v>
+      </c>
+      <c r="L80" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>17</v>
+      </c>
+      <c r="B81" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="E81">
+        <v>1</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>20</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81" t="s">
+        <v>16</v>
+      </c>
+      <c r="L81" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>18</v>
+      </c>
+      <c r="B82" t="s">
+        <v>12</v>
+      </c>
+      <c r="C82">
+        <v>0</v>
+      </c>
+      <c r="D82">
+        <v>1</v>
+      </c>
+      <c r="E82">
+        <v>1</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>4</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82" t="s">
+        <v>16</v>
+      </c>
+      <c r="L82" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>19</v>
+      </c>
+      <c r="B83" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83">
+        <v>0</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>1</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>4</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>2</v>
+      </c>
+      <c r="K83" t="s">
+        <v>16</v>
+      </c>
+      <c r="L83" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>20</v>
+      </c>
+      <c r="B84" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84">
+        <v>0</v>
+      </c>
+      <c r="D84">
+        <v>1</v>
+      </c>
+      <c r="E84">
+        <v>1</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>11</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>2</v>
+      </c>
+      <c r="K84" t="s">
+        <v>16</v>
+      </c>
+      <c r="L84" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>21</v>
+      </c>
+      <c r="B85" t="s">
+        <v>12</v>
+      </c>
+      <c r="C85">
+        <v>0</v>
+      </c>
+      <c r="D85">
+        <v>0</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="K85" t="s">
+        <v>16</v>
+      </c>
+      <c r="L85" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>22</v>
+      </c>
+      <c r="B86" t="s">
+        <v>12</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86">
+        <v>0</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>2</v>
+      </c>
+      <c r="K86" t="s">
+        <v>16</v>
+      </c>
+      <c r="L86" s="1">
+        <v>45963</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>1</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87">
+        <v>0</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>1</v>
+      </c>
+      <c r="K87" t="s">
+        <v>18</v>
+      </c>
+      <c r="L87" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>2</v>
+      </c>
+      <c r="B88" t="s">
+        <v>14</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88">
+        <v>0</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>1</v>
+      </c>
+      <c r="K88" t="s">
+        <v>18</v>
+      </c>
+      <c r="L88" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>3</v>
+      </c>
+      <c r="B89" t="s">
+        <v>12</v>
+      </c>
+      <c r="C89">
+        <v>1</v>
+      </c>
+      <c r="D89">
+        <v>0</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>1</v>
+      </c>
+      <c r="K89" t="s">
+        <v>18</v>
+      </c>
+      <c r="L89" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="B90" t="s">
+        <v>14</v>
+      </c>
+      <c r="C90">
+        <v>0</v>
+      </c>
+      <c r="D90">
+        <v>0</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>2</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90" t="s">
+        <v>18</v>
+      </c>
+      <c r="L90" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>5</v>
+      </c>
+      <c r="B91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>0</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="K91" t="s">
+        <v>18</v>
+      </c>
+      <c r="L91" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>6</v>
+      </c>
+      <c r="B92" t="s">
+        <v>14</v>
+      </c>
+      <c r="C92">
+        <v>0</v>
+      </c>
+      <c r="D92">
+        <v>0</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92">
+        <v>6</v>
+      </c>
+      <c r="I92">
+        <v>1</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92" t="s">
+        <v>18</v>
+      </c>
+      <c r="L92" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>7</v>
+      </c>
+      <c r="B93" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93">
+        <v>0</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="K93" t="s">
+        <v>18</v>
+      </c>
+      <c r="L93" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>8</v>
+      </c>
+      <c r="B94" t="s">
+        <v>14</v>
+      </c>
+      <c r="C94">
+        <v>0</v>
+      </c>
+      <c r="D94">
+        <v>0</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>1</v>
+      </c>
+      <c r="K94" t="s">
+        <v>18</v>
+      </c>
+      <c r="L94" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>9</v>
+      </c>
+      <c r="B95" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95">
+        <v>0</v>
+      </c>
+      <c r="D95">
+        <v>1</v>
+      </c>
+      <c r="E95">
+        <v>1</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>4</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95" t="s">
+        <v>18</v>
+      </c>
+      <c r="L95" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>10</v>
+      </c>
+      <c r="B96" t="s">
+        <v>14</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96">
+        <v>0</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>1</v>
+      </c>
+      <c r="J96">
+        <v>1</v>
+      </c>
+      <c r="K96" t="s">
+        <v>18</v>
+      </c>
+      <c r="L96" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>11</v>
+      </c>
+      <c r="B97" t="s">
+        <v>14</v>
+      </c>
+      <c r="C97">
+        <v>0</v>
+      </c>
+      <c r="D97">
+        <v>0</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="K97" t="s">
+        <v>18</v>
+      </c>
+      <c r="L97" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>12</v>
+      </c>
+      <c r="B98" t="s">
+        <v>14</v>
+      </c>
+      <c r="C98">
+        <v>1</v>
+      </c>
+      <c r="D98">
+        <v>0</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="K98" t="s">
+        <v>18</v>
+      </c>
+      <c r="L98" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>13</v>
+      </c>
+      <c r="B99" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99">
+        <v>0</v>
+      </c>
+      <c r="D99">
+        <v>0</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>1</v>
+      </c>
+      <c r="K99" t="s">
+        <v>18</v>
+      </c>
+      <c r="L99" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>14</v>
+      </c>
+      <c r="B100" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100">
+        <v>0</v>
+      </c>
+      <c r="D100">
+        <v>0</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="K100" t="s">
+        <v>18</v>
+      </c>
+      <c r="L100" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>15</v>
+      </c>
+      <c r="B101">
+        <v>16</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101">
+        <v>0</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>1</v>
+      </c>
+      <c r="K101" t="s">
+        <v>18</v>
+      </c>
+      <c r="L101" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102">
+        <v>16</v>
+      </c>
+      <c r="B102" t="s">
+        <v>12</v>
+      </c>
+      <c r="C102">
+        <v>0</v>
+      </c>
+      <c r="D102">
+        <v>1</v>
+      </c>
+      <c r="E102">
+        <v>1</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>4</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="K102" t="s">
+        <v>18</v>
+      </c>
+      <c r="L102" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103">
+        <v>17</v>
+      </c>
+      <c r="B103" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103">
+        <v>0</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
+      <c r="K103" t="s">
+        <v>18</v>
+      </c>
+      <c r="L103" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104">
+        <v>18</v>
+      </c>
+      <c r="B104" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104">
+        <v>0</v>
+      </c>
+      <c r="D104">
+        <v>0</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>1</v>
+      </c>
+      <c r="K104" t="s">
+        <v>18</v>
+      </c>
+      <c r="L104" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105">
+        <v>19</v>
+      </c>
+      <c r="B105" t="s">
+        <v>14</v>
+      </c>
+      <c r="C105">
+        <v>0</v>
+      </c>
+      <c r="D105">
+        <v>1</v>
+      </c>
+      <c r="E105">
+        <v>1</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>8</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="K105" t="s">
+        <v>18</v>
+      </c>
+      <c r="L105" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106">
+        <v>20</v>
+      </c>
+      <c r="B106" t="s">
+        <v>12</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106">
+        <v>0</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106">
+        <v>7</v>
+      </c>
+      <c r="I106">
+        <v>1</v>
+      </c>
+      <c r="J106">
+        <v>1</v>
+      </c>
+      <c r="K106" t="s">
+        <v>18</v>
+      </c>
+      <c r="L106" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107">
+        <v>21</v>
+      </c>
+      <c r="B107" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <v>0</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="K107" t="s">
+        <v>18</v>
+      </c>
+      <c r="L107" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108">
+        <v>1</v>
+      </c>
+      <c r="B108" t="s">
+        <v>14</v>
+      </c>
+      <c r="C108">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <v>0</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>2</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="K108" t="s">
+        <v>18</v>
+      </c>
+      <c r="L108" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109">
+        <v>2</v>
+      </c>
+      <c r="B109" t="s">
+        <v>19</v>
+      </c>
+      <c r="C109">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <v>0</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>2</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>2</v>
+      </c>
+      <c r="K109" t="s">
+        <v>18</v>
+      </c>
+      <c r="L109" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110">
+        <v>3</v>
+      </c>
+      <c r="B110" t="s">
+        <v>14</v>
+      </c>
+      <c r="C110">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <v>1</v>
+      </c>
+      <c r="E110">
+        <v>1</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>2</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>2</v>
+      </c>
+      <c r="K110" t="s">
+        <v>18</v>
+      </c>
+      <c r="L110" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111">
+        <v>4</v>
+      </c>
+      <c r="B111" t="s">
+        <v>14</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <v>0</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111" t="s">
+        <v>18</v>
+      </c>
+      <c r="L111" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A112">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>14</v>
+      </c>
+      <c r="C112">
+        <v>0</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>2</v>
+      </c>
+      <c r="K112" t="s">
+        <v>18</v>
+      </c>
+      <c r="L112" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113">
+        <v>6</v>
+      </c>
+      <c r="B113" t="s">
+        <v>12</v>
+      </c>
+      <c r="C113">
+        <v>0</v>
+      </c>
+      <c r="D113">
+        <v>0</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113" t="s">
+        <v>18</v>
+      </c>
+      <c r="L113" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A114">
+        <v>7</v>
+      </c>
+      <c r="B114" t="s">
+        <v>14</v>
+      </c>
+      <c r="C114">
+        <v>0</v>
+      </c>
+      <c r="D114">
+        <v>1</v>
+      </c>
+      <c r="E114">
+        <v>1</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>4</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>2</v>
+      </c>
+      <c r="K114" t="s">
+        <v>18</v>
+      </c>
+      <c r="L114" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A115">
+        <v>8</v>
+      </c>
+      <c r="B115" t="s">
+        <v>12</v>
+      </c>
+      <c r="C115">
+        <v>0</v>
+      </c>
+      <c r="D115">
+        <v>0</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>2</v>
+      </c>
+      <c r="K115" t="s">
+        <v>18</v>
+      </c>
+      <c r="L115" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A116">
+        <v>9</v>
+      </c>
+      <c r="B116" t="s">
+        <v>14</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116">
+        <v>0</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>2</v>
+      </c>
+      <c r="K116" t="s">
+        <v>18</v>
+      </c>
+      <c r="L116" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A117">
+        <v>10</v>
+      </c>
+      <c r="B117" t="s">
+        <v>14</v>
+      </c>
+      <c r="C117">
+        <v>0</v>
+      </c>
+      <c r="D117">
+        <v>0</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>2</v>
+      </c>
+      <c r="K117" t="s">
+        <v>18</v>
+      </c>
+      <c r="L117" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A118">
+        <v>11</v>
+      </c>
+      <c r="B118" t="s">
+        <v>15</v>
+      </c>
+      <c r="C118">
+        <v>0</v>
+      </c>
+      <c r="D118">
+        <v>0</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>2</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>2</v>
+      </c>
+      <c r="K118" t="s">
+        <v>18</v>
+      </c>
+      <c r="L118" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A119">
+        <v>12</v>
+      </c>
+      <c r="B119" t="s">
+        <v>14</v>
+      </c>
+      <c r="C119">
+        <v>0</v>
+      </c>
+      <c r="D119">
+        <v>0</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>2</v>
+      </c>
+      <c r="K119" t="s">
+        <v>18</v>
+      </c>
+      <c r="L119" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A120">
+        <v>13</v>
+      </c>
+      <c r="B120" t="s">
+        <v>14</v>
+      </c>
+      <c r="C120">
+        <v>0</v>
+      </c>
+      <c r="D120">
+        <v>0</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>1</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>1</v>
+      </c>
+      <c r="J120">
+        <v>2</v>
+      </c>
+      <c r="K120" t="s">
+        <v>18</v>
+      </c>
+      <c r="L120" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A121">
+        <v>14</v>
+      </c>
+      <c r="B121" t="s">
+        <v>15</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121">
+        <v>0</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>2</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>2</v>
+      </c>
+      <c r="K121" t="s">
+        <v>18</v>
+      </c>
+      <c r="L121" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A122">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>14</v>
+      </c>
+      <c r="C122">
+        <v>1</v>
+      </c>
+      <c r="D122">
+        <v>1</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>3</v>
+      </c>
+      <c r="I122">
+        <v>1</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122" t="s">
+        <v>18</v>
+      </c>
+      <c r="L122" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A123">
+        <v>16</v>
+      </c>
+      <c r="B123" t="s">
+        <v>12</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123">
+        <v>0</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+      <c r="K123" t="s">
+        <v>18</v>
+      </c>
+      <c r="L123" s="1">
+        <v>45964</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A124">
+        <v>17</v>
+      </c>
+      <c r="B124" t="s">
+        <v>14</v>
+      </c>
+      <c r="C124">
+        <v>0</v>
+      </c>
+      <c r="D124">
+        <v>0</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>1</v>
+      </c>
+      <c r="J124">
+        <v>2</v>
+      </c>
+      <c r="K124" t="s">
+        <v>18</v>
+      </c>
+      <c r="L124" s="1">
+        <v>45964</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:L124" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>